--- a/assets/pliki_bazy/polecane.xlsx
+++ b/assets/pliki_bazy/polecane.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\kiedy_biegam_app2\app_kb\pliki_bazy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\aplikacja_moj_bieg\app_kb\pliki_bazy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63124885-9699-4F93-AF02-CD374F21891D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371C9136-6245-4A63-98B9-E50BCCD7F0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35970" yWindow="2190" windowWidth="19620" windowHeight="10320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30870" yWindow="5715" windowWidth="20280" windowHeight="11055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>nazwa</t>
   </si>
@@ -45,89 +45,83 @@
     <t>link</t>
   </si>
   <si>
-    <t>10. Łańcucka Piętka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 km </t>
-  </si>
-  <si>
-    <t>Łańcut</t>
-  </si>
-  <si>
     <t>Podkarpackie</t>
   </si>
   <si>
-    <t>https://lancutbiega.pl/regulamin/</t>
-  </si>
-  <si>
-    <t>18. PKO Półmaraton Rzeszowski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.097 km </t>
-  </si>
-  <si>
     <t>Rzeszów</t>
   </si>
   <si>
-    <t>https://runrzeszow.pl/zapisy/polmaraton/</t>
-  </si>
-  <si>
-    <t>51 Maraton Dębno</t>
-  </si>
-  <si>
     <t>42.195 km</t>
   </si>
   <si>
-    <t>DĘBNO</t>
-  </si>
-  <si>
-    <t>11 Nocny Wrocław Półmaraton</t>
-  </si>
-  <si>
     <t>21.097 km</t>
   </si>
   <si>
-    <t>WROCŁAW</t>
-  </si>
-  <si>
-    <t>DOLNOŚLĄSKIE</t>
-  </si>
-  <si>
-    <t>11 Nocny Portowy Maraton Szczeciński</t>
-  </si>
-  <si>
-    <t>SZCZECIN</t>
-  </si>
-  <si>
-    <t>ZACHODNIOPOMORSKIE</t>
-  </si>
-  <si>
-    <t>48. Półmaraton Lechitów</t>
-  </si>
-  <si>
-    <t>GNIEZNO</t>
-  </si>
-  <si>
-    <t>WIELKOPOLSKIE</t>
-  </si>
-  <si>
-    <t>Gdyński Bieg Niepodległości</t>
-  </si>
-  <si>
     <t>10 km</t>
   </si>
   <si>
-    <t>GDYNIA</t>
-  </si>
-  <si>
-    <t>POMORSKIE</t>
+    <t>22. Cracovia Maraton</t>
+  </si>
+  <si>
+    <t>Kraków</t>
+  </si>
+  <si>
+    <t>Małopolskie</t>
+  </si>
+  <si>
+    <t>https://cracoviamaraton.pl/strona-glowna?hl=pl</t>
+  </si>
+  <si>
+    <t>Podkarpacki Festiwal Sportowy</t>
+  </si>
+  <si>
+    <t>21 km, 42 km, 63 km</t>
+  </si>
+  <si>
+    <t>https://podkarpackifestiwalsportowy.pl/</t>
+  </si>
+  <si>
+    <t>11. Nocny Wrocław Półmaraton</t>
+  </si>
+  <si>
+    <t>Wrocław</t>
+  </si>
+  <si>
+    <t>Dolnośląskie</t>
+  </si>
+  <si>
+    <t>https://mcs.wroc.pl/polmaraton/</t>
+  </si>
+  <si>
+    <t>Nocny Bieg Świętojański</t>
+  </si>
+  <si>
+    <t>Gdynia</t>
+  </si>
+  <si>
+    <t>Pomorskie</t>
+  </si>
+  <si>
+    <t>https://gdyniasport.pl/pl/imprezy/nocny-bieg-swietojanski</t>
+  </si>
+  <si>
+    <t>11. Nocny Portowy Maraton Szczeciński</t>
+  </si>
+  <si>
+    <t>Szczecin</t>
+  </si>
+  <si>
+    <t>Zachodniopomorskie</t>
+  </si>
+  <si>
+    <t>https://www.maratonszczecinski.pl/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,6 +133,22 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -150,7 +160,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -158,17 +168,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -451,14 +489,14 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34.90625" customWidth="1"/>
-    <col min="2" max="2" width="12.26953125" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" customWidth="1"/>
     <col min="3" max="3" width="11.6328125" customWidth="1"/>
     <col min="4" max="4" width="11.26953125" customWidth="1"/>
     <col min="5" max="5" width="29.54296875" customWidth="1"/>
     <col min="6" max="6" width="38.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -478,192 +516,174 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="4">
+        <v>45812</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="3">
-        <v>46153</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B3" s="4">
+        <v>45808</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="2" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="4">
+        <v>45822</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="4">
+        <v>45828</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1">
-        <v>45814</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="3">
-        <v>45822</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="3">
+      <c r="F5" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="4">
         <v>45857</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1">
-        <v>45899</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
+      <c r="D6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="3">
-        <v>45921</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="3">
-        <v>45972</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="A9" s="1"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+      <c r="A10" s="1"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+      <c r="A11" s="1"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="A12" s="1"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+      <c r="A13" s="1"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{3E099C44-FE62-4352-97F7-F88D13627F4E}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{AAE56B44-53A2-4A9E-9FC6-30435881DCCE}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{2B4E8CA8-3EB5-4710-BA6F-877A4317A04D}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{37D836BF-3682-4264-B91E-BF910F9292FD}"/>
+    <hyperlink ref="F6" r:id="rId5" xr:uid="{FCD3989A-17A5-4D85-92B8-41D84A199766}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
--- a/assets/pliki_bazy/polecane.xlsx
+++ b/assets/pliki_bazy/polecane.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\aplikacja_moj_bieg\app_kb\pliki_bazy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\aplikacja_moj_bieg\app_kb\assets\pliki_bazy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371C9136-6245-4A63-98B9-E50BCCD7F0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4959A5-A74B-4743-935D-8966A9F7A398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30870" yWindow="5715" windowWidth="20280" windowHeight="11055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31830" yWindow="2400" windowWidth="23055" windowHeight="12660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -521,7 +521,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="4">
-        <v>45812</v>
+        <v>45753</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>8</v>

--- a/assets/pliki_bazy/polecane.xlsx
+++ b/assets/pliki_bazy/polecane.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\aplikacja_moj_bieg\app_kb\assets\pliki_bazy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4959A5-A74B-4743-935D-8966A9F7A398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E28D4C5-DEFA-4E0D-8AE5-EB82211B9FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31830" yWindow="2400" windowWidth="23055" windowHeight="12660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/assets/pliki_bazy/polecane.xlsx
+++ b/assets/pliki_bazy/polecane.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\aplikacja_moj_bieg\app_kb\assets\pliki_bazy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E28D4C5-DEFA-4E0D-8AE5-EB82211B9FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E37EF6-3FE0-4421-9522-900B71883F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31830" yWindow="2400" windowWidth="23055" windowHeight="12660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>nazwa</t>
   </si>
@@ -115,18 +115,38 @@
   </si>
   <si>
     <t>https://www.maratonszczecinski.pl/</t>
+  </si>
+  <si>
+    <t>47. Maraton Warszawski</t>
+  </si>
+  <si>
+    <t>Warszawa</t>
+  </si>
+  <si>
+    <t>Mazowieckie</t>
+  </si>
+  <si>
+    <t>https://maratonwarszawski.com/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -160,7 +180,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -183,27 +203,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
@@ -616,12 +651,25 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="1"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="2">
+        <v>45928</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
@@ -682,8 +730,9 @@
     <hyperlink ref="F4" r:id="rId3" xr:uid="{2B4E8CA8-3EB5-4710-BA6F-877A4317A04D}"/>
     <hyperlink ref="F5" r:id="rId4" xr:uid="{37D836BF-3682-4264-B91E-BF910F9292FD}"/>
     <hyperlink ref="F6" r:id="rId5" xr:uid="{FCD3989A-17A5-4D85-92B8-41D84A199766}"/>
+    <hyperlink ref="F7" r:id="rId6" xr:uid="{8CC19A2F-EB2E-4CD7-AB70-8C55001D1562}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
--- a/assets/pliki_bazy/polecane.xlsx
+++ b/assets/pliki_bazy/polecane.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\aplikacja_moj_bieg\app_kb\assets\pliki_bazy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\aplikacja_moj_bieg\app_kb\pliki_bazy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E37EF6-3FE0-4421-9522-900B71883F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A822A26-0CD4-40E1-9D16-F4CADDCE11EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>nazwa</t>
   </si>
@@ -58,18 +58,6 @@
   </si>
   <si>
     <t>10 km</t>
-  </si>
-  <si>
-    <t>22. Cracovia Maraton</t>
-  </si>
-  <si>
-    <t>Kraków</t>
-  </si>
-  <si>
-    <t>Małopolskie</t>
-  </si>
-  <si>
-    <t>https://cracoviamaraton.pl/strona-glowna?hl=pl</t>
   </si>
   <si>
     <t>Podkarpacki Festiwal Sportowy</t>
@@ -235,7 +223,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
@@ -520,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34.90625" customWidth="1"/>
@@ -551,41 +539,41 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="4">
-        <v>45753</v>
+        <v>45808</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="5" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="4">
+        <v>45822</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="4">
-        <v>45808</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>6</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>17</v>
@@ -596,10 +584,10 @@
         <v>18</v>
       </c>
       <c r="B4" s="4">
-        <v>45822</v>
+        <v>45828</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>19</v>
@@ -607,7 +595,7 @@
       <c r="E4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -616,10 +604,10 @@
         <v>22</v>
       </c>
       <c r="B5" s="4">
-        <v>45828</v>
+        <v>45857</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>23</v>
@@ -627,49 +615,36 @@
       <c r="E5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="4">
-        <v>45857</v>
+      <c r="B6" s="2">
+        <v>45928</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="2">
-        <v>45928</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>33</v>
-      </c>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="1"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
@@ -677,6 +652,8 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
@@ -714,25 +691,15 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="1"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{3E099C44-FE62-4352-97F7-F88D13627F4E}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{AAE56B44-53A2-4A9E-9FC6-30435881DCCE}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{2B4E8CA8-3EB5-4710-BA6F-877A4317A04D}"/>
-    <hyperlink ref="F5" r:id="rId4" xr:uid="{37D836BF-3682-4264-B91E-BF910F9292FD}"/>
-    <hyperlink ref="F6" r:id="rId5" xr:uid="{FCD3989A-17A5-4D85-92B8-41D84A199766}"/>
-    <hyperlink ref="F7" r:id="rId6" xr:uid="{8CC19A2F-EB2E-4CD7-AB70-8C55001D1562}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{AAE56B44-53A2-4A9E-9FC6-30435881DCCE}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{2B4E8CA8-3EB5-4710-BA6F-877A4317A04D}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{37D836BF-3682-4264-B91E-BF910F9292FD}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{FCD3989A-17A5-4D85-92B8-41D84A199766}"/>
+    <hyperlink ref="F6" r:id="rId5" xr:uid="{8CC19A2F-EB2E-4CD7-AB70-8C55001D1562}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>